--- a/output/full_scan/batch_seq7_2026-06-29.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-29.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6585</v>
+        <v>6834</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>755.9095417351108</v>
+        <v>777.7178082529229</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>128.5</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.42827501358975</v>
+        <v>63.71892693592842</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>57.36018418324933</v>
+        <v>50.23201542278032</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.4659294763288347</v>
+        <v>0.1764116538903792</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-1.349543411523314</v>
+        <v>2.163599598758855</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6790</v>
+        <v>6585</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>701.0451872731353</v>
+        <v>755.9095417351108</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40.45</v>
+        <v>128.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.7170527968824</v>
+        <v>56.42827501358975</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.79288966689978</v>
+        <v>57.36018418324933</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5786405201455117</v>
+        <v>0.4659294763288347</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0812964055327447</v>
+        <v>-1.349543411523314</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6691</v>
+        <v>6790</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>694.6811406251036</v>
+        <v>701.0451872731353</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>795</v>
+        <v>40.45</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.62507551784468</v>
+        <v>58.7170527968824</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31.51789238804573</v>
+        <v>20.79288966689978</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.068114062510356</v>
+        <v>0.5786405201455117</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>11.99856187395438</v>
+        <v>0.0812964055327447</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6698</v>
+        <v>6691</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>686.0056419257595</v>
+        <v>694.6811406251036</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44.2</v>
+        <v>795</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.10733170392757</v>
+        <v>69.62507551784468</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.45522885265083</v>
+        <v>31.51789238804573</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6046260095372763</v>
+        <v>2.068114062510356</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1105862078837915</v>
+        <v>11.99856187395438</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6525</v>
+        <v>6698</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>682.124737493662</v>
+        <v>686.0056419257595</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>143</v>
+        <v>44.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.0716828998567</v>
+        <v>59.10733170392757</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34.96276380258284</v>
+        <v>35.45522885265083</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5366958224131934</v>
+        <v>0.6046260095372763</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.0584669596661</v>
+        <v>0.1105862078837915</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6757</v>
+        <v>6525</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>643.2953638886203</v>
+        <v>682.124737493662</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>61.3</v>
+        <v>143</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.03339595888547</v>
+        <v>57.0716828998567</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.45030261874881</v>
+        <v>34.96276380258284</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5787902945835661</v>
+        <v>0.5366958224131934</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5489306072573639</v>
+        <v>1.0584669596661</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6491</v>
+        <v>6757</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>637.2230893565379</v>
+        <v>643.2953638886203</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>331</v>
+        <v>61.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.09624001890154</v>
+        <v>59.03339595888547</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>23.48741730391857</v>
+        <v>35.45030261874881</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.437288475395606</v>
+        <v>0.5787902945835661</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3985461764670148</v>
+        <v>0.5489306072573639</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6645</v>
+        <v>6491</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>635.6481391409928</v>
+        <v>637.2230893565379</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16</v>
+        <v>331</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.36643985770652</v>
+        <v>63.09624001890154</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>49.52570026892574</v>
+        <v>23.48741730391857</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1393861506165334</v>
+        <v>1.437288475395606</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1704373583121731</v>
+        <v>-0.3985461764670148</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6589</v>
+        <v>6645</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>634.5836007141384</v>
+        <v>635.6481391409928</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>48.2</v>
+        <v>16</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.75840502643928</v>
+        <v>64.36643985770652</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16.37010737793116</v>
+        <v>49.52570026892574</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.333880858087112</v>
+        <v>0.1393861506165334</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3934513159676166</v>
+        <v>0.1704373583121731</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6664</v>
+        <v>6589</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>629.7861187030256</v>
+        <v>634.5836007141384</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>382</v>
+        <v>48.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45.86626281621308</v>
+        <v>62.75840502643928</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.96261605642883</v>
+        <v>16.37010737793116</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6574638091783314</v>
+        <v>1.333880858087112</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4803074601761583</v>
+        <v>0.3934513159676166</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6625</v>
+        <v>6664</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>627.5928945606116</v>
+        <v>629.7861187030256</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>382</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.31506235830774</v>
+        <v>45.86626281621308</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.99100357353765</v>
+        <v>24.96261605642883</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6851740024576977</v>
+        <v>0.6574638091783314</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1016160247090343</v>
+        <v>0.4803074601761583</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6684</v>
+        <v>6625</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>619.7935127281844</v>
+        <v>627.5928945606116</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.7533900057752</v>
+        <v>62.31506235830774</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.21041723767679</v>
+        <v>30.99100357353765</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.281220335426792</v>
+        <v>0.6851740024576977</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.261919379504476</v>
+        <v>0.1016160247090343</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6831</v>
+        <v>6684</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>613.9826782100794</v>
+        <v>619.7935127281844</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>794</v>
+        <v>58.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.5990816478825</v>
+        <v>63.7533900057752</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.27670814720756</v>
+        <v>36.21041723767679</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6809432861062678</v>
+        <v>1.281220335426792</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.274136357006185</v>
+        <v>1.261919379504476</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6668</v>
+        <v>6831</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>611.1313930637583</v>
+        <v>613.9826782100794</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>38.75</v>
+        <v>794</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45.51804980479417</v>
+        <v>55.5990816478825</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.88824502485584</v>
+        <v>27.27670814720756</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2175629038611259</v>
+        <v>0.6809432861062678</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.3678573696177278</v>
+        <v>0.274136357006185</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6742</v>
+        <v>6668</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>610.5385681696321</v>
+        <v>611.1313930637583</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>38.75</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.92381022732567</v>
+        <v>45.51804980479417</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>35.03501497535423</v>
+        <v>27.88824502485584</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5030168073075656</v>
+        <v>0.2175629038611259</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0869423559318498</v>
+        <v>-0.3678573696177278</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6579</v>
+        <v>6742</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>610.2031621471713</v>
+        <v>610.5385681696321</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>154</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46.30507469512068</v>
+        <v>55.92381022732567</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25.35899867864154</v>
+        <v>35.03501497535423</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2807613348828037</v>
+        <v>0.5030168073075656</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-2.544556931587872</v>
+        <v>-0.0869423559318498</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6743</v>
+        <v>6579</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>605.7200795615335</v>
+        <v>610.2031621471713</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>30.75</v>
+        <v>154</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.51873384876955</v>
+        <v>46.30507469512068</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.12872165818953</v>
+        <v>25.35899867864154</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.694676021114721</v>
+        <v>0.2807613348828037</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0678248941935507</v>
+        <v>-2.544556931587872</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6651</v>
+        <v>6743</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>600.8962951785584</v>
+        <v>605.7200795615335</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>144.5</v>
+        <v>30.75</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.57991543409029</v>
+        <v>61.51873384876955</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.78981049595416</v>
+        <v>21.12872165818953</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.800796966122454</v>
+        <v>2.694676021114721</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.2049409983917813</v>
+        <v>0.0678248941935507</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6494</v>
+        <v>6651</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>593.1705366158842</v>
+        <v>600.8962951785584</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>62.9</v>
+        <v>144.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.88973813047259</v>
+        <v>52.57991543409029</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.67060756321003</v>
+        <v>30.78981049595416</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2683826654327673</v>
+        <v>0.800796966122454</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0017228221611076</v>
+        <v>-0.2049409983917813</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6531</v>
+        <v>6494</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>590.9553472163465</v>
+        <v>593.1705366158842</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>980</v>
+        <v>62.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.01004590856478</v>
+        <v>53.88973813047259</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.40202353877358</v>
+        <v>33.67060756321003</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.590456863392691</v>
+        <v>0.2683826654327673</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-2.533998200342591</v>
+        <v>0.0017228221611076</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6666</v>
+        <v>6531</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>586.94869888119</v>
+        <v>590.9553472163465</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>43.4</v>
+        <v>980</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.97033361165128</v>
+        <v>49.01004590856478</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>39.31248104340907</v>
+        <v>26.40202353877358</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.31074201145064</v>
+        <v>0.590456863392691</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0857326394339875</v>
+        <v>-2.533998200342591</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6829</v>
+        <v>6666</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>581.8231483024729</v>
+        <v>586.94869888119</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>224.5</v>
+        <v>43.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.54720766419941</v>
+        <v>59.97033361165128</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14.76291469780364</v>
+        <v>39.31248104340907</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.123970287527067</v>
+        <v>0.31074201145064</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.092682366653549</v>
+        <v>0.0857326394339875</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6821</v>
+        <v>6829</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>576.2065378384593</v>
+        <v>581.8231483024729</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>61.8</v>
+        <v>224.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>47.66165674123264</v>
+        <v>56.54720766419941</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.2814113620662</v>
+        <v>14.76291469780364</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.100854733413789</v>
+        <v>1.123970287527067</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.061528124956787</v>
+        <v>2.092682366653549</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6753</v>
+        <v>6821</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>573.6777612383041</v>
+        <v>576.2065378384593</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>128.5</v>
+        <v>61.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.56601400811717</v>
+        <v>47.66165674123264</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13.90925128508779</v>
+        <v>19.2814113620662</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3.095306250444567</v>
+        <v>1.100854733413789</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.9306388884088196</v>
+        <v>-1.061528124956787</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6672</v>
+        <v>6753</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>568.7926833935333</v>
+        <v>573.6777612383041</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>281.5</v>
+        <v>128.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>69.1340720827267</v>
+        <v>55.56601400811717</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.8608908549953</v>
+        <v>13.90925128508779</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.006086064488629</v>
+        <v>3.095306250444567</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>5.419472431239814</v>
+        <v>0.9306388884088196</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6505</v>
+        <v>6672</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>564.988698061675</v>
+        <v>568.7926833935333</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>55.3</v>
+        <v>281.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.86006493887534</v>
+        <v>69.1340720827267</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13.31453892820276</v>
+        <v>34.8608908549953</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7272759272840399</v>
+        <v>1.006086064488629</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.2399630973615305</v>
+        <v>5.419472431239814</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6770</v>
+        <v>6505</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>563.578707948231</v>
+        <v>564.988698061675</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.43186618131192</v>
+        <v>55.86006493887534</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.58845029476664</v>
+        <v>13.31453892820276</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9747741351432178</v>
+        <v>0.7272759272840399</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3076010417743187</v>
+        <v>0.2399630973615305</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6719</v>
+        <v>6770</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>556.9478003775355</v>
+        <v>563.578707948231</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>261.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.61809649645317</v>
+        <v>55.43186618131192</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.62840995104552</v>
+        <v>25.58845029476664</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9384233827812362</v>
+        <v>0.9747741351432178</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.875533052264842</v>
+        <v>0.3076010417743187</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6642</v>
+        <v>6719</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>555.0579308830794</v>
+        <v>556.9478003775355</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>75.8</v>
+        <v>261.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>41.48890700586155</v>
+        <v>55.61809649645317</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40.57369425063968</v>
+        <v>39.62840995104552</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3941267462081348</v>
+        <v>0.9384233827812362</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.677186610925333</v>
+        <v>1.875533052264842</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6670</v>
+        <v>6642</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>552.9692055329429</v>
+        <v>555.0579308830794</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>249.5</v>
+        <v>75.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>38.0741802045801</v>
+        <v>41.48890700586155</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>31.20365452129341</v>
+        <v>40.57369425063968</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9844151136828098</v>
+        <v>0.3941267462081348</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-5.081420259858206</v>
+        <v>-1.677186610925333</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6517</v>
+        <v>6670</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>538.1866844281208</v>
+        <v>552.9692055329429</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>67.5</v>
+        <v>249.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.31318116786657</v>
+        <v>38.0741802045801</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.53752604333788</v>
+        <v>31.20365452129341</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2962588376999153</v>
+        <v>0.9844151136828098</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.643893357695311</v>
+        <v>-5.081420259858206</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6806</v>
+        <v>6517</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>533.7768356926886</v>
+        <v>538.1866844281208</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3.51</v>
+        <v>67.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>31.69502791374322</v>
+        <v>49.31318116786657</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.59319631657527</v>
+        <v>32.53752604333788</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.2962588376999153</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,48 +2213,48 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4112821527124572</v>
+        <v>-0.643893357695311</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6654</v>
+        <v>6806</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>532.8247793080529</v>
+        <v>533.7768356926886</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>187</v>
+        <v>3.51</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>59.93220284722404</v>
+        <v>31.69502791374322</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>47.5834418533197</v>
+        <v>32.59319631657527</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4008685691174602</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-3.459944685734989</v>
+        <v>0.4112821527124572</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6811</v>
+        <v>6654</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>529.075986018412</v>
+        <v>532.8247793080529</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>207.5</v>
+        <v>187</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>38.44448233802351</v>
+        <v>59.93220284722404</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.71996663084262</v>
+        <v>47.5834418533197</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3945616826172458</v>
+        <v>0.4008685691174602</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-3.998767324244504</v>
+        <v>-3.459944685734989</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6548</v>
+        <v>6811</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>520.7904152639086</v>
+        <v>529.075986018412</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>85</v>
+        <v>207.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.42581825046739</v>
+        <v>38.44448233802351</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>42.90658226074393</v>
+        <v>21.71996663084262</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8211406090003063</v>
+        <v>0.3945616826172458</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.568013786519538</v>
+        <v>-3.998767324244504</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6658</v>
+        <v>6548</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>515.3516384636487</v>
+        <v>520.7904152639086</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.64008964146862</v>
+        <v>55.42581825046739</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.22206786774358</v>
+        <v>42.90658226074393</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.213381314016326</v>
+        <v>0.8211406090003063</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.061915348826837</v>
+        <v>-1.568013786519538</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6667</v>
+        <v>6658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>513.73190153161</v>
+        <v>515.3516384636487</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>260.5</v>
+        <v>213</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.65793881574669</v>
+        <v>64.64008964146862</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12.16687516849184</v>
+        <v>28.22206786774358</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3543894853299445</v>
+        <v>1.213381314016326</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-2.054808475034185</v>
+        <v>1.061915348826837</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6782</v>
+        <v>6667</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>510.5255663775174</v>
+        <v>513.73190153161</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>195</v>
+        <v>260.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.84690078687201</v>
+        <v>43.65793881574669</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8.110478584917482</v>
+        <v>12.16687516849184</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6867956136959027</v>
+        <v>0.3543894853299445</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2984589910773227</v>
+        <v>-2.054808475034185</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6716</v>
+        <v>6782</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>504.508837451896</v>
+        <v>510.5255663775174</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>91.2</v>
+        <v>195</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.13429071186602</v>
+        <v>49.84690078687201</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.35834460566629</v>
+        <v>8.110478584917482</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3772420896801229</v>
+        <v>0.6867956136959027</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.8882225784272493</v>
+        <v>0.2984589910773227</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6799</v>
+        <v>6716</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>498.2347015227581</v>
+        <v>504.508837451896</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>96.7</v>
+        <v>91.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>49.53570633913086</v>
+        <v>43.13429071186602</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.75019095956443</v>
+        <v>24.35834460566629</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3758793643825644</v>
+        <v>0.3772420896801229</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3203821033973304</v>
+        <v>-0.8882225784272493</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6582</v>
+        <v>6799</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>489.3590947224401</v>
+        <v>498.2347015227581</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>33.2</v>
+        <v>96.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>68.27623854762381</v>
+        <v>49.53570633913086</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30.78969574753311</v>
+        <v>25.75019095956443</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8104086371715561</v>
+        <v>0.3758793643825644</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2031960312911894</v>
+        <v>0.3203821033973304</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6573</v>
+        <v>6715</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>476.0075052670933</v>
+        <v>493.6694982051503</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>19.75</v>
+        <v>424</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>65.81904696958181</v>
+        <v>45.78362718828079</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.40076937577074</v>
+        <v>22.2509991660573</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8673358193898539</v>
+        <v>0.4175393942805054</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.437229455013876</v>
+        <v>0.4496838857457543</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6570</v>
+        <v>6582</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>471.2802451514788</v>
+        <v>489.3590947224401</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>49.25</v>
+        <v>33.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>38.99481632721918</v>
+        <v>68.27623854762381</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24.87755774104919</v>
+        <v>30.78969574753311</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4642117781258542</v>
+        <v>0.8104086371715561</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.348594028334015</v>
+        <v>0.2031960312911894</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6695</v>
+        <v>6573</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>470.1617084659391</v>
+        <v>476.0075052670933</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>58.9</v>
+        <v>19.75</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.12739858437237</v>
+        <v>65.81904696958181</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>29.29471898881113</v>
+        <v>23.40076937577074</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5816991207402402</v>
+        <v>0.8673358193898539</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4544496948018852</v>
+        <v>0.437229455013876</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6725</v>
+        <v>6570</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>464.8700107936007</v>
+        <v>471.2802451514788</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>318</v>
+        <v>49.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.11617646822985</v>
+        <v>38.99481632721918</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.72651210036686</v>
+        <v>24.87755774104919</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4719150687429612</v>
+        <v>0.4642117781258542</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.579770915923334</v>
+        <v>-1.348594028334015</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6556</v>
+        <v>6695</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>464.6278965660301</v>
+        <v>470.1617084659391</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>71.8</v>
+        <v>58.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.49411558554803</v>
+        <v>53.12739858437237</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>37.41090649595603</v>
+        <v>29.29471898881113</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3476064884246091</v>
+        <v>0.5816991207402402</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1794191644302456</v>
+        <v>0.4544496948018852</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6530</v>
+        <v>6725</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>461.0087571818869</v>
+        <v>464.8700107936007</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>85.2</v>
+        <v>318</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.88499612442175</v>
+        <v>49.11617646822985</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.23606639554053</v>
+        <v>22.72651210036686</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4243953269706556</v>
+        <v>0.4719150687429612</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.459256563665825</v>
+        <v>1.579770915923334</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6515</v>
+        <v>6556</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>440.6608691503969</v>
+        <v>464.6278965660301</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>8015</v>
+        <v>71.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>38.15925166502361</v>
+        <v>50.49411558554803</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.48138342654435</v>
+        <v>37.41090649595603</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.0086864752286</v>
+        <v>0.3476064884246091</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-95.19399435782675</v>
+        <v>-0.1794191644302456</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6788</v>
+        <v>6530</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>425.0230842004652</v>
+        <v>461.0087571818869</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>422.5</v>
+        <v>85.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.95928873689233</v>
+        <v>33.88499612442175</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.156393375793877</v>
+        <v>20.23606639554053</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3050937379140702</v>
+        <v>0.4243953269706556</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.8345136200191781</v>
+        <v>-1.459256563665825</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6526</v>
+        <v>6515</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>422.7821245116321</v>
+        <v>440.6608691503969</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>636</v>
+        <v>8015</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.87944796757331</v>
+        <v>38.15925166502361</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.06221441681287</v>
+        <v>18.48138342654435</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6124175045937502</v>
+        <v>1.0086864752286</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-4.132620700782782</v>
+        <v>-95.19399435782675</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6679</v>
+        <v>6788</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>416.0092347315433</v>
+        <v>425.0230842004652</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>258</v>
+        <v>422.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>36.96300627352148</v>
+        <v>47.95928873689233</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.99823694012463</v>
+        <v>8.156393375793877</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8971722000047327</v>
+        <v>0.3050937379140702</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.003298746147399</v>
+        <v>-0.8345136200191781</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6792</v>
+        <v>6526</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>412.7318620795108</v>
+        <v>422.7821245116321</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>62.2</v>
+        <v>636</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.80766016124426</v>
+        <v>44.87944796757331</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.92271671441449</v>
+        <v>15.06221441681287</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5268299828677828</v>
+        <v>0.6124175045937502</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.9839112941570364</v>
+        <v>-4.132620700782782</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6592</v>
+        <v>6679</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>401.906219437471</v>
+        <v>416.0092347315433</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.27508897370911</v>
+        <v>36.96300627352148</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>27.01223151910514</v>
+        <v>18.99823694012463</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.384698441247728</v>
+        <v>0.8971722000047327</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2143858266396693</v>
+        <v>-1.003298746147399</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6498</v>
+        <v>6792</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>401.6587341096581</v>
+        <v>412.7318620795108</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>91.8</v>
+        <v>62.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>37.22823964497119</v>
+        <v>40.80766016124426</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.06633616560955</v>
+        <v>26.92271671441449</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7004205493119482</v>
+        <v>0.5268299828677828</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.256544809411426</v>
+        <v>-0.9839112941570364</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6588</v>
+        <v>6592</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>377.9405876337929</v>
+        <v>401.906219437471</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>27.80717860865215</v>
+        <v>49.27508897370911</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.10331316271288</v>
+        <v>27.01223151910514</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.200294908668785</v>
+        <v>1.384698441247728</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.9992201191053028</v>
+        <v>-0.2143858266396693</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6538</v>
+        <v>6498</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>377.197689692074</v>
+        <v>401.6587341096581</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>119.5</v>
+        <v>91.8</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.09959282472669</v>
+        <v>37.22823964497119</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>32.16621556260775</v>
+        <v>26.06633616560955</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4383404965822137</v>
+        <v>0.7004205493119482</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2135613968254741</v>
+        <v>-1.256544809411426</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6560</v>
+        <v>6588</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>376.3987464311768</v>
+        <v>377.9405876337929</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>38.4</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.20501790077601</v>
+        <v>27.80717860865215</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.41987933124276</v>
+        <v>17.10331316271288</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3458672702555864</v>
+        <v>1.200294908668785</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1202328458995865</v>
+        <v>-0.9992201191053028</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6640</v>
+        <v>6538</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>374.9986964348704</v>
+        <v>377.197689692074</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1035</v>
+        <v>119.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.00937293067033</v>
+        <v>54.09959282472669</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.15880010344958</v>
+        <v>32.16621556260775</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7552378290419985</v>
+        <v>0.4383404965822137</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.555548800664056</v>
+        <v>0.2135613968254741</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6510</v>
+        <v>6560</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>367.847948181955</v>
+        <v>376.3987464311768</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>3035</v>
+        <v>38.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>38.71660295319398</v>
+        <v>49.20501790077601</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.23915444784465</v>
+        <v>23.41987933124276</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6860685426020752</v>
+        <v>0.3458672702555864</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-30.44303312737215</v>
+        <v>0.1202328458995865</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6720</v>
+        <v>6640</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>365.8802370174906</v>
+        <v>374.9986964348704</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>135.5</v>
+        <v>1035</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24.00985594022456</v>
+        <v>38.00937293067033</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>31.5307627112587</v>
+        <v>25.15880010344958</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4284780853689158</v>
+        <v>0.7552378290419985</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.5965359480648296</v>
+        <v>-1.555548800664056</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6756</v>
+        <v>6510</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>364.4606083695749</v>
+        <v>367.847948181955</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>94</v>
+        <v>3035</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.70017778628332</v>
+        <v>38.71660295319398</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.2006826397815</v>
+        <v>16.23915444784465</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5463408951887135</v>
+        <v>0.6860685426020752</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.7389920592393315</v>
+        <v>-30.44303312737215</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6550</v>
+        <v>6720</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>360.8038690962432</v>
+        <v>365.8802370174906</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>13.25</v>
+        <v>135.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.19571815183851</v>
+        <v>24.00985594022456</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.62723965397048</v>
+        <v>31.5307627112587</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.9236734559249066</v>
+        <v>0.4284780853689158</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1561077121436125</v>
+        <v>-0.5965359480648296</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6546</v>
+        <v>6756</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>355.0150451757609</v>
+        <v>364.4606083695749</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>36.75758320385611</v>
+        <v>44.70017778628332</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.67750624090366</v>
+        <v>23.2006826397815</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4142882697460511</v>
+        <v>0.5463408951887135</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.081997953259232</v>
+        <v>-0.7389920592393315</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6692</v>
+        <v>6550</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>343.4566110011236</v>
+        <v>360.8038690962432</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>26.35</v>
+        <v>13.25</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.23264298805852</v>
+        <v>42.19571815183851</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.8626852850858</v>
+        <v>29.62723965397048</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4974582425562817</v>
+        <v>0.9236734559249066</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2055006968278787</v>
+        <v>0.1561077121436125</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6781</v>
+        <v>6546</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>343.1852935784312</v>
+        <v>355.0150451757609</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1130</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.36226954725005</v>
+        <v>36.75758320385611</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.70974429326155</v>
+        <v>15.67750624090366</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5895921967126735</v>
+        <v>0.4142882697460511</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-3.59000896824768</v>
+        <v>-1.081997953259232</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6584</v>
+        <v>6692</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>342.4894188990017</v>
+        <v>343.4566110011236</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>685</v>
+        <v>26.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.00709936423584</v>
+        <v>46.23264298805852</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.43267200457316</v>
+        <v>16.8626852850858</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7836920195600503</v>
+        <v>0.4974582425562817</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>9.777926505505636</v>
+        <v>0.2055006968278787</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6727</v>
+        <v>6781</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>339.6401254206452</v>
+        <v>343.1852935784312</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>400</v>
+        <v>1130</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.57622092910104</v>
+        <v>47.36226954725005</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.94905216146091</v>
+        <v>11.70974429326155</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3723037804620475</v>
+        <v>0.5895921967126735</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-4.890129023591498</v>
+        <v>-3.59000896824768</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6532</v>
+        <v>6584</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>339.0552892187724</v>
+        <v>342.4894188990017</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>685</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.96435656393807</v>
+        <v>54.00709936423584</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.22219837712949</v>
+        <v>14.43267200457316</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3646591893555401</v>
+        <v>0.7836920195600503</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.272608493273665</v>
+        <v>9.777926505505636</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6669</v>
+        <v>6727</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>332.2368688157852</v>
+        <v>339.6401254206452</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>4580</v>
+        <v>400</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.11204519674797</v>
+        <v>41.57622092910104</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.6922261008222</v>
+        <v>15.94905216146091</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.036591150239351</v>
+        <v>0.3723037804620475</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-90.51851954446052</v>
+        <v>-4.890129023591498</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6708</v>
+        <v>6532</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>327.0773230317154</v>
+        <v>339.0552892187724</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>40.4</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.8175912052562</v>
+        <v>42.96435656393807</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.34024116096127</v>
+        <v>19.22219837712949</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7252520596609097</v>
+        <v>0.3646591893555401</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.139639831985592</v>
+        <v>-0.272608493273665</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6512</v>
+        <v>6669</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>321.8322088545739</v>
+        <v>332.2368688157852</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>19.95</v>
+        <v>4580</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.34257433129171</v>
+        <v>42.11204519674797</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.684630481868894</v>
+        <v>18.6922261008222</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4232748695307042</v>
+        <v>1.036591150239351</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2985238324802355</v>
+        <v>-90.51851954446052</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6598</v>
+        <v>6708</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>318.3393595568166</v>
+        <v>327.0773230317154</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>22.85</v>
+        <v>40.4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>34.22980754977395</v>
+        <v>51.8175912052562</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.65862457757158</v>
+        <v>15.34024116096127</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6533881170540795</v>
+        <v>0.7252520596609097</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2473886658118223</v>
+        <v>0.139639831985592</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6840</v>
+        <v>6512</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>317.8054330681196</v>
+        <v>321.8322088545739</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>61.3</v>
+        <v>19.95</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>38.37582277693629</v>
+        <v>52.34257433129171</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.86543663173396</v>
+        <v>7.684630481868894</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5470618522749566</v>
+        <v>0.4232748695307042</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6152083475234125</v>
+        <v>0.2985238324802355</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6568</v>
+        <v>6598</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>309.5524648538517</v>
+        <v>318.3393595568166</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>158.5</v>
+        <v>22.85</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>29.7951891918097</v>
+        <v>34.22980754977395</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.97302919925237</v>
+        <v>21.65862457757158</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.474551718915847</v>
+        <v>0.6533881170540795</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.002218525148788</v>
+        <v>-0.2473886658118223</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6823</v>
+        <v>6840</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>304.7415484917861</v>
+        <v>317.8054330681196</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.09254496750573</v>
+        <v>38.37582277693629</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.78160505638185</v>
+        <v>15.86543663173396</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6452934146959612</v>
+        <v>0.5470618522749566</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.4282574253279616</v>
+        <v>-0.6152083475234125</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6706</v>
+        <v>6830</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>302.4864455556673</v>
+        <v>314.3870191611209</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>140.5</v>
+        <v>502</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>33.94929977359189</v>
+        <v>38.39913467979579</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.13171864425145</v>
+        <v>20.41791085253952</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4382327107504625</v>
+        <v>0.2766899333010476</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-4.340937316480908</v>
+        <v>0.3240155762069463</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6606</v>
+        <v>6568</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>297.26471344469</v>
+        <v>309.5524648538517</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>24.7</v>
+        <v>158.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>37.51059549460607</v>
+        <v>29.7951891918097</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.82234556526465</v>
+        <v>29.97302919925237</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1349935872323572</v>
+        <v>0.474551718915847</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1853703969717167</v>
+        <v>-1.002218525148788</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6739</v>
+        <v>6823</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>294.9221243124545</v>
+        <v>304.7415484917861</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>996</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>33.75414777249394</v>
+        <v>39.09254496750573</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.15643851717525</v>
+        <v>20.78160505638185</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.97627599110186</v>
+        <v>0.6452934146959612</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-9.842869165476388</v>
+        <v>0.4282574253279616</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6690</v>
+        <v>6706</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>294.6306359281551</v>
+        <v>302.4864455556673</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>160.5</v>
+        <v>140.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>32.19111222741306</v>
+        <v>33.94929977359189</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.94925453810853</v>
+        <v>17.13171864425145</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3194931696693724</v>
+        <v>0.4382327107504625</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-2.24288028345357</v>
+        <v>-4.340937316480908</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6803</v>
+        <v>6606</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>288.2009912324209</v>
+        <v>297.26471344469</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>288.5</v>
+        <v>24.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>53.86963560101101</v>
+        <v>37.51059549460607</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>29.13973156113752</v>
+        <v>18.82234556526465</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9528223849139134</v>
+        <v>0.1349935872323572</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1981585155363859</v>
+        <v>-0.1853703969717167</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6789</v>
+        <v>6739</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>288.0634881865275</v>
+        <v>294.9221243124545</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>497.5</v>
+        <v>996</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.51117460612507</v>
+        <v>33.75414777249394</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.06393250028952</v>
+        <v>11.15643851717525</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4958762670169972</v>
+        <v>0.97627599110186</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2192287858848174</v>
+        <v>-9.842869165476388</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6643</v>
+        <v>6690</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.1336907968433</v>
+        <v>294.6306359281551</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>458.5</v>
+        <v>160.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>35.14239361346749</v>
+        <v>32.19111222741306</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.76493173668199</v>
+        <v>18.94925453810853</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5000065865042713</v>
+        <v>0.3194931696693724</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.470684251490482</v>
+        <v>-2.24288028345357</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6776</v>
+        <v>6803</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>285.0797049900448</v>
+        <v>288.2009912324209</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>53.7</v>
+        <v>288.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>27.9275505457741</v>
+        <v>53.86963560101101</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.34996256394346</v>
+        <v>29.13973156113752</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6545068146001258</v>
+        <v>0.9528223849139134</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.7388530651576475</v>
+        <v>0.1981585155363859</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6680</v>
+        <v>6789</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>284.8632887118135</v>
+        <v>288.0634881865275</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>48.4</v>
+        <v>497.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.83035062368615</v>
+        <v>45.51117460612507</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>5.095389873805117</v>
+        <v>16.06393250028952</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.788058328090816</v>
+        <v>0.4958762670169972</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5085484358944031</v>
+        <v>0.2192287858848174</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6504</v>
+        <v>6643</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>284.6558828208863</v>
+        <v>286.1336907968433</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>35.75</v>
+        <v>458.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>35.42382541633556</v>
+        <v>35.14239361346749</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.24240220089955</v>
+        <v>22.76493173668199</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3591939649353184</v>
+        <v>0.5000065865042713</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1155062219126692</v>
+        <v>-1.470684251490482</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6735</v>
+        <v>6776</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>283.62001575215</v>
+        <v>285.0797049900448</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>86</v>
+        <v>53.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>36.97171847940711</v>
+        <v>27.9275505457741</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.25593412424084</v>
+        <v>14.34996256394346</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6214290438395963</v>
+        <v>0.6545068146001258</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3874785945018422</v>
+        <v>-0.7388530651576475</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6805</v>
+        <v>6680</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>274.0185898679911</v>
+        <v>284.8632887118135</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1625</v>
+        <v>48.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.82622245964088</v>
+        <v>49.83035062368615</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.06199455159085</v>
+        <v>5.095389873805117</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.361585913261388</v>
+        <v>1.788058328090816</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-18.15774420328256</v>
+        <v>0.5085484358944031</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6558</v>
+        <v>6504</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>271.1174682566975</v>
+        <v>284.6558828208863</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>28.1</v>
+        <v>35.75</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.12198615650576</v>
+        <v>35.42382541633556</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.12637152953882</v>
+        <v>17.24240220089955</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2458004070462642</v>
+        <v>0.3591939649353184</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.4443131347088725</v>
+        <v>0.1155062219126692</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6768</v>
+        <v>6735</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>268.683217300332</v>
+        <v>283.62001575215</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>29.53225167246991</v>
+        <v>36.97171847940711</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.44020677879615</v>
+        <v>13.25593412424084</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6135006030166543</v>
+        <v>0.6214290438395963</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.739290023170959</v>
+        <v>-0.3874785945018422</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6577</v>
+        <v>6805</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>259.5504580125903</v>
+        <v>274.0185898679911</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>72.3</v>
+        <v>1625</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>23.04796575297578</v>
+        <v>38.82622245964088</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>23.23724807431638</v>
+        <v>13.06199455159085</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3550458012590313</v>
+        <v>0.361585913261388</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.7888892405110851</v>
+        <v>-18.15774420328256</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6534</v>
+        <v>6558</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>258.036017175938</v>
+        <v>271.1174682566975</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>90.3</v>
+        <v>28.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.11147045249481</v>
+        <v>36.12198615650576</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.98348741972752</v>
+        <v>22.12637152953882</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2210896227512858</v>
+        <v>0.2458004070462642</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0572804443248291</v>
+        <v>-0.4443131347088725</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6761</v>
+        <v>6768</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>252.8528459689207</v>
+        <v>268.683217300332</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.35420779288301</v>
+        <v>29.53225167246991</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.39399478914218</v>
+        <v>18.44020677879615</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3230827304153587</v>
+        <v>0.6135006030166543</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.855135649462464</v>
+        <v>-1.739290023170959</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6591</v>
+        <v>6577</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.53716449436</v>
+        <v>259.5504580125903</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>52.9</v>
+        <v>72.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.73882524283894</v>
+        <v>23.04796575297578</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.26778608590005</v>
+        <v>23.23724807431638</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3976905112547524</v>
+        <v>0.3550458012590313</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.261322915280394</v>
+        <v>-0.7888892405110851</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6605</v>
+        <v>6534</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>250.2299983265081</v>
+        <v>258.036017175938</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>139</v>
+        <v>90.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.71375616602791</v>
+        <v>43.11147045249481</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.38691324163607</v>
+        <v>13.98348741972752</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.02326533220039</v>
+        <v>0.2210896227512858</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.9297615723125152</v>
+        <v>0.0572804443248291</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6754</v>
+        <v>6761</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>243.8932213993311</v>
+        <v>252.8528459689207</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>44.25</v>
+        <v>180</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.17890649832546</v>
+        <v>39.35420779288301</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.27283857524559</v>
+        <v>17.39399478914218</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4020294799974027</v>
+        <v>0.3230827304153587</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.090217031162532</v>
+        <v>-2.855135649462464</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6541</v>
+        <v>6591</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>243.2642954044576</v>
+        <v>252.53716449436</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>39.3</v>
+        <v>52.9</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.66281197933444</v>
+        <v>38.73882524283894</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.5003978094662</v>
+        <v>21.26778608590005</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.119913187692684</v>
+        <v>0.3976905112547524</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1408687843340156</v>
+        <v>-0.261322915280394</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6796</v>
+        <v>6605</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>236.5700449363722</v>
+        <v>250.2299983265081</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>55.7</v>
+        <v>139</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>30.93035645034258</v>
+        <v>49.71375616602791</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>31.02206445675964</v>
+        <v>15.38691324163607</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.840162550598442</v>
+        <v>1.02326533220039</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0519806167755452</v>
+        <v>-0.9297615723125152</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6732</v>
+        <v>6754</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>229.5114697325638</v>
+        <v>243.8932213993311</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>162</v>
+        <v>44.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.65123841928588</v>
+        <v>42.17890649832546</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.94948246775046</v>
+        <v>20.27283857524559</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3888152579506713</v>
+        <v>0.4020294799974027</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.4106331577023724</v>
+        <v>-0.090217031162532</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6597</v>
+        <v>6541</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.3372734700236</v>
+        <v>243.2642954044576</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>67</v>
+        <v>39.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.9064507086946</v>
+        <v>45.66281197933444</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.01820568506363</v>
+        <v>17.5003978094662</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.1251435226869099</v>
+        <v>1.119913187692684</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.4570717119907248</v>
+        <v>-0.1408687843340156</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6657</v>
+        <v>6796</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>225.4888230387785</v>
+        <v>236.5700449363722</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.1</v>
+        <v>55.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.35883058932669</v>
+        <v>30.93035645034258</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.4892594875334</v>
+        <v>31.02206445675964</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2474628249130312</v>
+        <v>0.840162550598442</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1514033381461188</v>
+        <v>-0.0519806167755452</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6771</v>
+        <v>6732</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>220.4662845617223</v>
+        <v>229.5114697325638</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>38.15</v>
+        <v>162</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>19.96843194468286</v>
+        <v>47.65123841928588</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>20.51403767887583</v>
+        <v>18.94948246775046</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6447375462803042</v>
+        <v>0.3888152579506713</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3610231592182462</v>
+        <v>0.4106331577023724</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6614</v>
+        <v>6597</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>216.7893225811034</v>
+        <v>227.3372734700236</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.65</v>
+        <v>67</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.92210215946298</v>
+        <v>45.9064507086946</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.9993574143167</v>
+        <v>10.01820568506363</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.44046876355997</v>
+        <v>0.1251435226869099</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0364646667940116</v>
+        <v>-0.4570717119907248</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6581</v>
+        <v>6657</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>202.6948043570332</v>
+        <v>225.4888230387785</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>106</v>
+        <v>36.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.2754423595798</v>
+        <v>45.35883058932669</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.4221177907186</v>
+        <v>22.4892594875334</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2037815522084189</v>
+        <v>0.2474628249130312</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.355968322347803</v>
+        <v>0.1514033381461188</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6794</v>
+        <v>6771</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>199.0087595619974</v>
+        <v>220.4662845617223</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>79</v>
+        <v>38.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.95833133163212</v>
+        <v>19.96843194468286</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.13681745423441</v>
+        <v>20.51403767887583</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8390218402833767</v>
+        <v>0.6447375462803042</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1620950337311271</v>
+        <v>-0.3610231592182462</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6533</v>
+        <v>6614</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>197.1570018277712</v>
+        <v>216.7893225811034</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>191</v>
+        <v>39.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.4788608401544</v>
+        <v>44.92210215946298</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.05229152127714</v>
+        <v>15.9993574143167</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5108627455809505</v>
+        <v>0.44046876355997</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.032511547672515</v>
+        <v>-0.0364646667940116</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6671</v>
+        <v>6581</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>194.7440662454286</v>
+        <v>202.6948043570332</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>24.4</v>
+        <v>106</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>24.2156039526181</v>
+        <v>40.2754423595798</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.32841592942492</v>
+        <v>11.4221177907186</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2756723430317853</v>
+        <v>0.2037815522084189</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0492587321795533</v>
+        <v>-0.355968322347803</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6624</v>
+        <v>6794</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>190.7893295489273</v>
+        <v>199.0087595619973</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>40.75</v>
+        <v>79</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.94069409688484</v>
+        <v>43.95833133163212</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.86602278629512</v>
+        <v>14.13681745423441</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1581565252407377</v>
+        <v>0.8390218402833767</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0527668559429135</v>
+        <v>-0.1620950337311271</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6741</v>
+        <v>6533</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>183.7236777088129</v>
+        <v>197.1570018277712</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>60.6</v>
+        <v>191</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.90055912996193</v>
+        <v>36.4788608401544</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.4091940518684</v>
+        <v>13.05229152127714</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8784593159854114</v>
+        <v>0.5108627455809505</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0613724837590332</v>
+        <v>-1.032511547672515</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6763</v>
+        <v>6671</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>182.4618961881009</v>
+        <v>194.7440662454286</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>46.8</v>
+        <v>24.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.57225036942821</v>
+        <v>24.2156039526181</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.68188162278445</v>
+        <v>27.32841592942492</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2279383000030607</v>
+        <v>0.2756723430317853</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0899963930003346</v>
+        <v>-0.0492587321795533</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6722</v>
+        <v>6624</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>180.5429817724702</v>
+        <v>190.7893295489273</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>35.75</v>
+        <v>40.75</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.38088190419485</v>
+        <v>50.94069409688484</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.72324079009837</v>
+        <v>10.86602278629512</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4997517944905434</v>
+        <v>0.1581565252407377</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3144709806321437</v>
+        <v>-0.0527668559429135</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6486</v>
+        <v>6741</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>175.2339880754658</v>
+        <v>183.7236777088129</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>80.8</v>
+        <v>60.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.5941998201265</v>
+        <v>42.90055912996193</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.26492284935577</v>
+        <v>10.4091940518684</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5102906597503056</v>
+        <v>0.8784593159854114</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0122036956903209</v>
+        <v>-0.0613724837590332</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6641</v>
+        <v>6763</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>158.2436511346509</v>
+        <v>182.4618961881009</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.95</v>
+        <v>46.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.34915932563149</v>
+        <v>49.57225036942821</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.87398932595232</v>
+        <v>18.68188162278445</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7132940499840943</v>
+        <v>0.2279383000030607</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0363251220384129</v>
+        <v>-0.0899963930003346</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6807</v>
+        <v>6722</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>149.670424655758</v>
+        <v>180.5429817724702</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>33.45</v>
+        <v>35.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.29211586512572</v>
+        <v>37.38088190419485</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.9438203242251</v>
+        <v>24.72324079009837</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7939252389428691</v>
+        <v>0.4997517944905434</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1040643609179861</v>
+        <v>-0.3144709806321437</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6674</v>
+        <v>6486</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>148.3952662427903</v>
+        <v>175.2339880754658</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.1</v>
+        <v>80.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.6742683298748</v>
+        <v>39.5941998201265</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.93451261299305</v>
+        <v>13.26492284935577</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3053802351545812</v>
+        <v>0.5102906597503056</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0277847025328646</v>
+        <v>-0.0122036956903209</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6838</v>
+        <v>6641</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>145.1398892911319</v>
+        <v>158.2436511346509</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>24.1</v>
+        <v>17.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.72001950779999</v>
+        <v>40.34915932563149</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.03882588165741</v>
+        <v>16.87398932595232</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8450985309876704</v>
+        <v>0.7132940499840943</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0349642624332783</v>
+        <v>-0.0363251220384129</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6552</v>
+        <v>6807</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>139.3877401449186</v>
+        <v>149.670424655758</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>29</v>
+        <v>33.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.8615731430143</v>
+        <v>46.29211586512572</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.34089058850025</v>
+        <v>19.9438203242251</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3707193762847114</v>
+        <v>0.7939252389428691</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2250395729773311</v>
+        <v>0.1040643609179861</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6655</v>
+        <v>6674</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>128.2116851410553</v>
+        <v>148.3952662427903</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>122.5</v>
+        <v>17.1</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>50.77774551132021</v>
+        <v>42.6742683298748</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.75502014012048</v>
+        <v>17.93451261299305</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3215468490013857</v>
+        <v>0.3053802351545812</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.534069572155774</v>
+        <v>-0.0277847025328646</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6689</v>
+        <v>6838</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>125.4379313096106</v>
+        <v>145.1398892911319</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>63</v>
+        <v>24.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>33.04248460196811</v>
+        <v>38.72001950779999</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.88737343302632</v>
+        <v>14.03882588165741</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2922874962721402</v>
+        <v>0.8450985309876704</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.5660385911814232</v>
+        <v>-0.0349642624332783</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6835</v>
+        <v>6552</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>107.374125821292</v>
+        <v>139.3877401449186</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>35.15</v>
+        <v>29</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>34.35984272220269</v>
+        <v>42.8615731430143</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.54566337092412</v>
+        <v>14.34089058850025</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4653411429458972</v>
+        <v>0.3707193762847114</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,62 +6824,221 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1212598198322379</v>
+        <v>-0.2250395729773311</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
+        <v>6655</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>科定</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>128.2116851410553</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>50.77774551132021</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>12.75502014012048</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.3215468490013857</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>1.534069572155774</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>125.4379313096106</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>33.04248460196811</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>13.88737343302632</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.2922874962721402</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.5660385911814232</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>圓裕</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>107.374125821292</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>34.35984272220269</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>17.54566337092412</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.4653411429458972</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.1212598198322379</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
         <v>6561</v>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>是方</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
         <v>56.90075385894571</v>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E124" s="2" t="n">
         <v>337</v>
       </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
         <v>42.13620247484533</v>
       </c>
-      <c r="I121" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>16.33899960831414</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>0.8453321018190449</v>
       </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
         <v>-1.129515376265373</v>
       </c>
-      <c r="O121" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
